--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olankade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olankade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olankade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KFTKG</t>
+          <t>HDMFA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Grundläggande filmproduktion för Manus för film och TV` (15 hp); rad: - Grundläggande filmproduktion för Manus för film och TV, 15 hp</t>
+          <t>Programtext `Samhällsvetenskapliga metoder III – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder III - inriktning statsvetenskap` (kurskod `ASK289`); rad: - [[ASK289|Samhällsvetenskapliga metoder III – inriktning statsvetenskap]], 15 hp</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HDMFA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>KFTKG</t>
+          <t>KAPSG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Dokumentär metod för filmisk gestaltning` (7,5 hp); rad: - Dokumentär metod för filmisk gestaltning, 7,5 hp</t>
+          <t>Programtext `Konceptutveckling inom medieproduktion för Ljud- och musikproduktion` ≠ kursplanens namn `Konceptutveckling inom medieproduktion för Ljud- och musikproduktion` (kurskod `GLP2NK`); rad: - [[GLP2NK|Konceptutveckling inom medieproduktion för Ljud- och musikproduktion]], 7,5 hp</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`7` (5 hp); rad: - 7, 5 hp</t>
+          <t>`Grundläggande filmproduktion för Manus för film och TV` (15 hp); rad: - Grundläggande filmproduktion för Manus för film och TV, 15 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
+          <t>`Dokumentär metod för filmisk gestaltning` (7,5 hp); rad: - Dokumentär metod för filmisk gestaltning, 7,5 hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
+          <t>`7` (5 hp); rad: - 7, 5 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KFTPG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
+          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
+          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
+          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
+          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
+          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
+          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i musik­ och ljuddesign` (15 hp); rad: - Examensarbete för högskoleexamen i musik­ och ljuddesign, 15 hp</t>
+          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
+          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
+          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen i musik­ och ljuddesign` (15 hp); rad: - Examensarbete för högskoleexamen i musik­ och ljuddesign, 15 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
+          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
+          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>Programtext `Utveckling och lärande för ämneslärare årskurs 7–9 - AIL` ≠ kursplanens namn `Utveckling och lärande för ämneslärare årskurs 7-9 - AIL` (kurskod `GPG3AE`); rad: - &lt;a class="no-graph" href="GPG3AE"&gt;Utveckling och lärande för ämneslärare årskurs 7–9 - AIL&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>Programtext `Bedömning och betygssättning för ämneslärare årskurs 7–9 - AIL` ≠ kursplanens namn `Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL` (kurskod `APG2AB`); rad: - &lt;a class="no-graph" href="APG2AB"&gt;Bedömning och betygssättning för ämneslärare årskurs 7–9 - AIL&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>Programtext `Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7–9` ≠ kursplanens namn `Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AIH237`); rad: - [[AIH237|Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7–9]], 15 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>Programtext `Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` ≠ kursplanens namn `Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AMD239`); rad: - &lt;a class="no-graph" href="AMD239"&gt;Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - [[GPG3CK|Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6]], 15 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Bullet beskriver val mellan flera kurser</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Valbar Inriktningskurs` (15hp); rad: - Valbar Inriktningskurs, 15hp</t>
+          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SMHTA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Eller Examensarbete för Magisterexamen i Turismvetenskap` (15 hp); rad: - Eller Examensarbete för Magisterexamen i Turismvetenskap, 15 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMHTA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SMHTA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`Studenterna väljer valfria kurser, i valfritt ämne nationellt eller internationellt, i enlighet med eget intresse och i samråd med programansvarig. Ett antal valfria kurser om` (30 hp); rad: - Studenterna väljer valfria kurser, i valfritt ämne nationellt eller internationellt, i enlighet med eget intresse och i samråd med programansvarig. Ett antal valfria kurser om, 30 hp</t>
+          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMHTA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2399,24 +2399,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
+          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,44 +2809,881 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>SFIFA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Bullet beskriver val mellan flera kurser</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>`Valbar Inriktningskurs` (15hp); rad: - Valbar Inriktningskurs, 15hp</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SFIFA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SMHTA</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Bullet beskriver val mellan flera kurser</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>`Eller Examensarbete för Magisterexamen i Turismvetenskap` (15 hp); rad: - Eller Examensarbete för Magisterexamen i Turismvetenskap, 15 hp</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMHTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SMHTA</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bullet beskriver val mellan flera kurser</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>`Studenterna väljer valfria kurser, i valfritt ämne nationellt eller internationellt, i enlighet med eget intresse och i samråd med programansvarig. Ett antal valfria kurser om` (30 hp); rad: - Studenterna väljer valfria kurser, i valfritt ämne nationellt eller internationellt, i enlighet med eget intresse och i samråd med programansvarig. Ett antal valfria kurser om, 30 hp</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMHTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SMINA</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SMINA</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Programtext avviker från kursplanens namn</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Programtext `Samhällsvetenskapliga metoder I – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder I - inriktning statsvetenskap` (kurskod `GSK2PT`); rad: - [[GSK2PT|Samhällsvetenskapliga metoder I – inriktning statsvetenskap]], 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
           <t>STMGG</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
         <is>
           <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E89"/>
+  <autoFilter ref="A1:E120"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3024,6 +3861,68 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
